--- a/נסיון.xlsx
+++ b/נסיון.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\libraries 7_08_11\Documents\Ithamar\Cognition research\MEMORY CLINIC\טיפולים מתקדמים לאלצהיימר AD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{575876D0-B150-4C80-A631-E3DB868E68F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{481466C8-F3D7-466A-9CA9-F205FDB8C997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{0B4BD74A-D09C-4E50-907E-F21BFC031CC5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="52">
   <si>
     <t>תעודת זהות</t>
   </si>
@@ -189,6 +189,12 @@
   </si>
   <si>
     <t>פרץ</t>
+  </si>
+  <si>
+    <t>חדוה</t>
+  </si>
+  <si>
+    <t>פוט</t>
   </si>
 </sst>
 </file>
@@ -561,7 +567,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{508C9257-8BB0-4C39-B154-820592AF736E}">
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="10" max="10" width="13.5" bestFit="1" customWidth="1"/>
@@ -1207,6 +1213,38 @@
         <v>45</v>
       </c>
     </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>54</v>
+      </c>
+      <c r="C21" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" t="s">
+        <v>51</v>
+      </c>
+      <c r="E21" t="s">
+        <v>38</v>
+      </c>
+      <c r="F21">
+        <v>6</v>
+      </c>
+      <c r="G21" t="s">
+        <v>41</v>
+      </c>
+      <c r="H21">
+        <v>9</v>
+      </c>
+      <c r="I21" t="s">
+        <v>45</v>
+      </c>
+      <c r="J21" t="s">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
